--- a/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21710" windowHeight="11120"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="物流信息" sheetId="1" r:id="rId1"/>
@@ -88,28 +88,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>物流跟踪号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>提单号</t>
-    </r>
+    <t>运单号</t>
+  </si>
+  <si>
+    <t>柜号</t>
   </si>
   <si>
     <r>
@@ -149,24 +131,16 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>物流跟踪号</t>
+      <t>运单号</t>
     </r>
   </si>
   <si>
@@ -228,7 +202,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,6 +366,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1182,12 +1162,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="9" width="13.3636363636364" customWidth="1"/>
+    <col min="1" max="9" width="13.3666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:9">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1235,12 +1215,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="6" width="16.0909090909091" customWidth="1"/>
+    <col min="1" max="6" width="16.0916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:6">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="物流信息" sheetId="1" r:id="rId1"/>
@@ -43,12 +43,21 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>发货</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>来源单</t>
+      <t>单</t>
     </r>
   </si>
   <si>
@@ -130,18 +139,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>运单号</t>
-    </r>
+    <t>发货单</t>
   </si>
   <si>
     <r>
@@ -212,7 +210,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -220,6 +217,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -366,12 +370,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -710,137 +708,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -849,6 +847,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1161,14 +1165,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="9" width="13.3666666666667" customWidth="1"/>
+    <col min="1" max="7" width="13.3666666666667" customWidth="1"/>
+    <col min="8" max="8" width="21.25" customWidth="1"/>
+    <col min="9" max="9" width="13.3666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -1196,13 +1202,20 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2" spans="8:8">
+      <c r="H2" s="4"/>
+    </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
       <formula1>"空运,快递,海运散装,海运整柜,铁运散装,铁运整柜"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
       <formula1>"待下单,已下单,运输中,已到港,已签收"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+      <formula1>40544</formula1>
+      <formula2>47849</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1220,12 +1233,12 @@
     <col min="1" max="6" width="16.0916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" ht="14.25" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>10</v>
@@ -1241,6 +1254,16 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576 D2:D1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999900</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="物流信息" sheetId="1" r:id="rId1"/>
@@ -31,13 +31,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -47,7 +40,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>发货</t>
+      <t>来源</t>
     </r>
     <r>
       <rPr>
@@ -139,7 +132,7 @@
     </r>
   </si>
   <si>
-    <t>发货单</t>
+    <t>来源单</t>
   </si>
   <si>
     <r>
@@ -1233,7 +1226,7 @@
     <col min="1" max="6" width="16.0916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>

--- a/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="11775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="物流信息" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -180,6 +187,21 @@
         <scheme val="minor"/>
       </rPr>
       <t>预估费用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>币种</t>
     </r>
   </si>
 </sst>
@@ -1166,7 +1188,7 @@
     <col min="9" max="9" width="13.3666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" ht="14.25" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1220,13 +1242,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="6" width="16.0916666666667" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" ht="14.25" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1244,17 +1267,20 @@
       </c>
       <c r="F1" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576 D2:D1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999</formula2>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:D1048576">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/fmLogistics.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="物流信息" sheetId="1" r:id="rId1"/>
@@ -31,22 +31,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>来源</t>
     </r>
     <r>
@@ -57,8 +41,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>单</t>
-    </r>
+      <t>单号</t>
+    </r>
+  </si>
+  <si>
+    <t>业务单号</t>
   </si>
   <si>
     <r>
@@ -139,33 +126,15 @@
     </r>
   </si>
   <si>
-    <t>来源单</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>实际重量</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>实际体积重</t>
-    </r>
-  </si>
-  <si>
+    <t>来源单号</t>
+  </si>
+  <si>
+    <t>物流运单号</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -179,6 +148,9 @@
   </si>
   <si>
     <r>
+      <t>*</t>
+    </r>
+    <r>
       <rPr>
         <sz val="10"/>
         <color theme="1"/>
@@ -186,11 +158,18 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>预估费用</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>预估费用金额</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -231,14 +210,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1180,55 +1159,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="7" width="13.3666666666667" customWidth="1"/>
-    <col min="8" max="8" width="21.25" customWidth="1"/>
-    <col min="9" max="9" width="13.3666666666667" customWidth="1"/>
+    <col min="1" max="8" width="13.3666666666667" customWidth="1"/>
+    <col min="9" max="9" width="21.25" customWidth="1"/>
+    <col min="10" max="10" width="13.3666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:9">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="8:8">
-      <c r="H2" s="4"/>
+    <row r="2" spans="9:9">
+      <c r="I2" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2">
       <formula1>"空运,快递,海运散装,海运整柜,铁运散装,铁运整柜"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>"待下单,已下单,运输中,已到港,已签收"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
       <formula1>40544</formula1>
       <formula2>47849</formula2>
     </dataValidation>
@@ -1242,45 +1224,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="6" width="16.0916666666667" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="1" max="5" width="16.0916666666667" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>0</formula1>
       <formula2>99999999999999900</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:D1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
